--- a/dcf/DLO.xlsx
+++ b/dcf/DLO.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1131,25 +1131,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>23.40745055623275</v>
+        <v>19.18407466400053</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>22.66490225205004</v>
+        <v>18.61217308441682</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>21.95520029703362</v>
+        <v>18.06529546597482</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>21.27670753477003</v>
+        <v>17.54220067472038</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>20.62787630353082</v>
+        <v>17.04171524593693</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>20.00724314325262</v>
+        <v>16.56272938810053</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>19.41342383828379</v>
+        <v>16.10419324008027</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>24.72071519191755</v>
+        <v>20.17169252669927</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>23.92056745010254</v>
+        <v>19.55647429033419</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>23.15603280844464</v>
+        <v>18.96836070214521</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>22.42532976212821</v>
+        <v>18.4060020734691</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>21.72677442419745</v>
+        <v>17.86812249377279</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>21.05877474237137</v>
+        <v>17.35351546598827</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>20.41982508317905</v>
+        <v>16.8610398188222</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>26.03397982760233</v>
+        <v>21.15931038939801</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>25.17623264815504</v>
+        <v>20.50077549625157</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>24.35686531985567</v>
+        <v>19.8714259383156</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>23.5739519894864</v>
+        <v>19.26980347221782</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>22.82567254486408</v>
+        <v>18.69452974160865</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>22.11030634149012</v>
+        <v>18.144301543876</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>21.4262263280743</v>
+        <v>17.61788639756412</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>27.34724446328713</v>
+        <v>22.14692825209674</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>26.43189784620754</v>
+        <v>21.44507670216895</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>25.55769783126669</v>
+        <v>20.77449117448599</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>24.72257421684459</v>
+        <v>20.13360487096654</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>23.92457066553072</v>
+        <v>19.52093698944451</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>23.16183794060887</v>
+        <v>18.93508762176374</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>22.43262757296955</v>
+        <v>18.37473297630605</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>28.66050909897192</v>
+        <v>23.13454611479547</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>27.68756304426003</v>
+        <v>22.38937790808633</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>26.75853034267771</v>
+        <v>21.67755641065638</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>25.87119644420277</v>
+        <v>20.99740626971526</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>25.02346878619734</v>
+        <v>20.34734423728038</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>24.21336953972762</v>
+        <v>19.72587369965148</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>23.4390288178648</v>
+        <v>19.13157955504797</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>29.97377373465671</v>
+        <v>24.12216397749421</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>28.94322824231253</v>
+        <v>23.3336791140037</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>27.95936285408874</v>
+        <v>22.58062164682677</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>27.01981867156097</v>
+        <v>21.86120766846398</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>26.12236690686398</v>
+        <v>21.17375148511624</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>25.26490113884637</v>
+        <v>20.51665977753921</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>24.44543006276006</v>
+        <v>19.8884261337899</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>31.2870383703415</v>
+        <v>25.10978184019294</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>30.19889344036503</v>
+        <v>24.27798031992108</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>29.16019536549976</v>
+        <v>23.48368688299716</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>28.16844089891914</v>
+        <v>22.7250090672127</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>27.22126502753061</v>
+        <v>22.0001587329521</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>26.31643273796512</v>
+        <v>21.30744585542695</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>25.4518313076553</v>
+        <v>20.64527271253182</v>
       </c>
     </row>
     <row r="13">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1.038230344419008</v>
+        <v>1.043928928206251</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>24.72257421684459</v>
+        <v>20.13360487096654</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>33.28833980657849</v>
+        <v>26.28399112209605</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>18.33711528506726</v>
+        <v>15.42553641778811</v>
       </c>
     </row>
     <row r="59">
